--- a/Coupang_Top20_20260607.xlsx
+++ b/Coupang_Top20_20260607.xlsx
@@ -462,266 +462,266 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Apple USB-C 커넥터 EarPods</t>
+          <t>한경희생활과학 초미세풍 발터치 리모컨 선풍기</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26990</v>
+        <v>39900</v>
       </c>
       <c r="C3">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8300107736&amp;itemId=25246423475&amp;vendorItemId=90965273088&amp;traceid=V0-113-6d3bd893a0f3e865", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8049298764&amp;itemId=22568615219&amp;vendorItemId=89610481080&amp;traceid=V0-113-c6225c8b32161464", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한경희생활과학 초미세풍 발터치 리모컨 선풍기</t>
+          <t>아이리버 C타입-C타입 패브릭 초고속 충전 데이터 케이블 60W</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39900</v>
+        <v>5090</v>
       </c>
       <c r="C4">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8049298764&amp;itemId=22568615219&amp;vendorItemId=89610481080&amp;traceid=V0-113-c6225c8b32161464", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8803472212&amp;itemId=25636725400&amp;vendorItemId=92626790654&amp;traceid=V0-113-4e0e1cdf04169745", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>아이리버 C타입-C타입 패브릭 초고속 충전 데이터 케이블 60W</t>
+          <t>Apple 2025 에어팟 프로 3 USB-C 블루투스 이어폰</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5090</v>
+        <v>335790</v>
       </c>
       <c r="C5">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8803472212&amp;itemId=25636725400&amp;vendorItemId=92626790654&amp;traceid=V0-113-4e0e1cdf04169745", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9024163013&amp;itemId=26462308675&amp;vendorItemId=93437588392&amp;traceid=V0-113-848acafd9e852dbc", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>알리사 100단 아이스 터보 MAX 휴대용 선풍기</t>
+          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26970</v>
+        <v>8800</v>
       </c>
       <c r="C6">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8719219704&amp;itemId=25325956860&amp;vendorItemId=92859054401&amp;traceid=V0-113-3390c08a48f3cae9", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홈플래닛 발터치 리모컨 스탠드형 선풍기</t>
+          <t>브리타 정수기 필터 막스트라 프로 퓨어 퍼포먼스 3입</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33890</v>
+        <v>21560</v>
       </c>
       <c r="C7">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1459643219&amp;itemId=2511597502&amp;vendorItemId=92134731921&amp;traceid=V0-113-62386184a6cb7f37", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9102889885&amp;itemId=23756832465&amp;vendorItemId=90781295338&amp;traceid=V0-113-59ae32451442015d", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
+          <t>아이리버 C타입-C타입 패브릭 초고속 충전 데이터 케이블 60W</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8800</v>
+        <v>5400</v>
       </c>
       <c r="C8">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8803472212&amp;itemId=25636725403&amp;vendorItemId=92626790675&amp;traceid=V0-113-4e0e1cdf04169745", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>브리타 정수기 필터 막스트라 프로 퓨어 퍼포먼스 3입</t>
+          <t>신지모루 오피디 25W GaN 듀얼포트 PPS 초고속 PD 충전기</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21560</v>
+        <v>8980</v>
       </c>
       <c r="C9">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9102889885&amp;itemId=23756832465&amp;vendorItemId=90781295338&amp;traceid=V0-113-59ae32451442015d", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7415163807&amp;itemId=19222022188&amp;vendorItemId=86338760049&amp;traceid=V0-113-693c11efc2bbce39", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>로지텍 G102IC 2세대 LIGHTSYNC 게이밍 유선마우스</t>
+          <t>홈플래닛 핸디형 스탠드 스팀다리미</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21160</v>
+        <v>28990</v>
       </c>
       <c r="C10">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6011227725&amp;itemId=28238141798&amp;vendorItemId=70778258892&amp;traceid=V0-113-38d0e1f44bf0cf88", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=310080038&amp;itemId=977484067&amp;vendorItemId=5392665218&amp;traceid=V0-113-c73a6d2a7fbf4b52", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>아이리버 C타입-C타입 패브릭 초고속 충전 데이터 케이블 60W</t>
+          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5400</v>
+        <v>19900</v>
       </c>
       <c r="C11">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8803472212&amp;itemId=25636725403&amp;vendorItemId=92626790675&amp;traceid=V0-113-4e0e1cdf04169745", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>신지모루 오피디 25W GaN 듀얼포트 PPS 초고속 PD 충전기</t>
+          <t>Apple 정품 20W USB-C 전원 어댑터 MUW13KH/A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8980</v>
+        <v>19800</v>
       </c>
       <c r="C12">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7415163807&amp;itemId=19222022188&amp;vendorItemId=86338760049&amp;traceid=V0-113-693c11efc2bbce39", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=2270230024&amp;itemId=22170383583&amp;vendorItemId=88946948908&amp;traceid=V0-113-fad4b0f7464d90db", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>홈플래닛 핸디형 스탠드 스팀다리미</t>
+          <t>원스탑 제로갭 슬림 개별 스위치 멀티탭 3구 16A + 안전커버</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28990</v>
+        <v>10260</v>
       </c>
       <c r="C13">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=310080038&amp;itemId=977484067&amp;vendorItemId=5392665218&amp;traceid=V0-113-c73a6d2a7fbf4b52", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8826084661&amp;itemId=25719073639&amp;vendorItemId=92787518032&amp;traceid=V0-113-b805d07925969125", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>홈플래닛 퀄컴 공식인증 QC3.0 18W 고속충전기 + C타입 충전케이블 1.2m 세트</t>
+          <t>유닉스 세라믹 판고데기</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7490</v>
+        <v>24900</v>
       </c>
       <c r="C14">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1628630781&amp;itemId=2778296479&amp;vendorItemId=89645323681&amp;traceid=V0-113-e16801aaf71b1d25", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8729115745&amp;itemId=25361584612&amp;vendorItemId=3089081003&amp;traceid=V0-113-c054456fc302c5b1", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
+          <t>홈플래닛 25W PPS PD 3.0 초고속 충전기 + CtoC 케이블 1.2m</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19900</v>
+        <v>7290</v>
       </c>
       <c r="C15">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5047898639&amp;itemId=6804859657&amp;vendorItemId=74097543659&amp;traceid=V0-113-482c6187a1b37f79", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Apple 정품 20W USB-C 전원 어댑터 MUW13KH/A</t>
+          <t>액센 프리미엄 캐릭터 마이크로 SD카드</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19800</v>
+        <v>18500</v>
       </c>
       <c r="C16">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=2270230024&amp;itemId=22170383583&amp;vendorItemId=88946948908&amp;traceid=V0-113-fad4b0f7464d90db", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7704604385&amp;itemId=6156844140&amp;vendorItemId=73453040955&amp;traceid=V0-113-a6ffe7d8068452b2", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>에이케이리빙 유파 발터치 리모컨 선풍기</t>
+          <t>번개표 개별스위치 멀티탭 2구</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35800</v>
+        <v>9900</v>
       </c>
       <c r="C17">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8225143195&amp;itemId=23653576267&amp;vendorItemId=92283755564&amp;traceid=V0-113-ba7b61a7e8a8ec65", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8528238769&amp;itemId=675697424&amp;vendorItemId=4741399345&amp;traceid=V0-113-ea50ce308ffdd129", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>원스탑 제로갭 슬림 개별 스위치 멀티탭 3구 16A + 안전커버</t>
+          <t>Apple 정품 라이트닝 이어팟</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10260</v>
+        <v>27000</v>
       </c>
       <c r="C18">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8826084661&amp;itemId=25719073639&amp;vendorItemId=92787518032&amp;traceid=V0-113-b805d07925969125", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5001745972&amp;itemId=23686271502&amp;vendorItemId=90711442673&amp;traceid=V0-113-57599c7d00aef45d", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>홈플래닛 패브릭 고속충전케이블 C타입</t>
+          <t>셀루미 메가 스틱 올인원 스마트폰 셀카봉 삼각대 171.7cm</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3690</v>
+        <v>12900</v>
       </c>
       <c r="C19">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8989759590&amp;itemId=26331343093&amp;vendorItemId=93308600079&amp;traceid=V0-113-47345bb1d46cbad4", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8915242678&amp;itemId=26046876968&amp;vendorItemId=93028357799&amp;traceid=V0-113-32aa3336abf6cce1", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>카스토리 벽걸이 에어컨 바람막이 걸이형 길이조절</t>
+          <t>신지모루 C to C PD 고속충전 케이블 60W</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5950</v>
+        <v>6900</v>
       </c>
       <c r="C20">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9544352055&amp;itemId=17793481362&amp;vendorItemId=95473605448&amp;traceid=V0-113-45ed21b6e37ef741", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9344838202&amp;itemId=13761827932&amp;vendorItemId=81012487257&amp;traceid=V0-113-0a9564caf484529f", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>엔보우 모노미니 탁상용 무선 선풍기</t>
+          <t>아이리버 3.5mm AUX 갤럭시 노트북 컴퓨터 알루미늄 커널형 유선 이어폰, BHC-70M, 블랙</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14900</v>
+        <v>7830</v>
       </c>
       <c r="C21">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8159651990&amp;itemId=23257490210&amp;vendorItemId=90463026195&amp;traceid=V0-113-0d14e8f2b8929e3d", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8602654934&amp;itemId=24944896878&amp;vendorItemId=91980127301&amp;traceid=V0-113-cef1a24c3259468a", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
